--- a/App/dataset/Cluster_dataset.xlsx
+++ b/App/dataset/Cluster_dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elyon\OneDrive\Desktop\Cosmo-Edu_Lab\dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elyon\OneDrive\Desktop\phd_PE\dark_matter_notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4BC1D9-BD30-41F7-B6BF-980F7C65A338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31693393-585C-4C05-A8C0-64866A31FF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abell0080" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,25 @@
     <sheet name="Abell3921" sheetId="14" r:id="rId14"/>
     <sheet name="Abell4067" sheetId="15" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="16">
   <si>
     <t>Radeg</t>
   </si>
@@ -54,9 +67,6 @@
     <t>bmag</t>
   </si>
   <si>
-    <t>Luminous_Mass_Msun</t>
-  </si>
-  <si>
     <t>Radius_kpc</t>
   </si>
   <si>
@@ -66,13 +76,25 @@
     <t>Total_Mass [M_sun]</t>
   </si>
   <si>
-    <t xml:space="preserve">Max_Radius [kpc] </t>
-  </si>
-  <si>
     <t>Standard_Deviation (km/s)</t>
   </si>
   <si>
-    <t>Lum_Mass_Tot [M_sun]</t>
+    <t>Star_Mass_Msun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean_Radius [kpc] </t>
+  </si>
+  <si>
+    <t>Gas_Mass[M_sun]</t>
+  </si>
+  <si>
+    <t>Star_Mass_Tot [M_sun]</t>
+  </si>
+  <si>
+    <t>Luminous_Mass[M_sun]</t>
+  </si>
+  <si>
+    <t>Tot_Mass/Lum_Mass</t>
   </si>
 </sst>
 </file>
@@ -520,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -532,13 +554,16 @@
     <col min="7" max="7" width="20.6640625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" customWidth="1"/>
-    <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="11" max="11" width="24.5546875" customWidth="1"/>
+    <col min="12" max="12" width="19.109375" customWidth="1"/>
+    <col min="13" max="13" width="23.21875" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="22.88671875" customWidth="1"/>
+    <col min="16" max="16" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,28 +583,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>8.5430399999999995</v>
       </c>
@@ -607,8 +641,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>8.5946700000000007</v>
       </c>
@@ -634,7 +672,7 @@
         <v>4187.0171717129369</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>8.6209199999999999</v>
       </c>
@@ -660,7 +698,7 @@
         <v>3067.6780714831029</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>8.6216699999999999</v>
       </c>
@@ -686,7 +724,7 @@
         <v>3103.038180063133</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>8.67258</v>
       </c>
@@ -712,7 +750,7 @@
         <v>4283.6701635460959</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8.6996699999999993</v>
       </c>
@@ -738,7 +776,7 @@
         <v>3039.198400719215</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8.7282100000000007</v>
       </c>
@@ -764,7 +802,7 @@
         <v>2872.6725330697332</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8.7654200000000007</v>
       </c>
@@ -790,7 +828,7 @@
         <v>3547.558827674286</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8.7673799999999993</v>
       </c>
@@ -816,7 +854,7 @@
         <v>3374.695973939215</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8.7730800000000002</v>
       </c>
@@ -842,7 +880,7 @@
         <v>2830.075593295031</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>8.7884200000000003</v>
       </c>
@@ -868,7 +906,7 @@
         <v>2201.2151608618078</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>8.8015799999999995</v>
       </c>
@@ -894,7 +932,7 @@
         <v>2094.512693653217</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>8.8297500000000007</v>
       </c>
@@ -920,7 +958,7 @@
         <v>2090.1294548778801</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>8.8450799999999994</v>
       </c>
@@ -946,7 +984,7 @@
         <v>2358.7594568599611</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>8.8529599999999995</v>
       </c>
@@ -3372,20 +3410,23 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3405,28 +3446,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>13.63439</v>
       </c>
@@ -3454,8 +3504,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>13.68092</v>
       </c>
@@ -3481,7 +3535,7 @@
         <v>4013.136209702659</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>13.74117</v>
       </c>
@@ -3507,7 +3561,7 @@
         <v>3422.303301395375</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>13.830730000000001</v>
       </c>
@@ -3533,7 +3587,7 @@
         <v>3159.0473007335831</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>13.85904</v>
       </c>
@@ -3559,7 +3613,7 @@
         <v>3958.8749314895408</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>13.897309999999999</v>
       </c>
@@ -3585,7 +3639,7 @@
         <v>2901.879922332736</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>13.89823</v>
       </c>
@@ -3611,7 +3665,7 @@
         <v>3741.9894763068401</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>13.90704</v>
       </c>
@@ -3637,7 +3691,7 @@
         <v>3292.4370281692809</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>13.948169999999999</v>
       </c>
@@ -3663,7 +3717,7 @@
         <v>2736.6423283225781</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>13.97434</v>
       </c>
@@ -3689,7 +3743,7 @@
         <v>4704.0910031398689</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>14.00521</v>
       </c>
@@ -3715,7 +3769,7 @@
         <v>4213.6469206008314</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>14.03429</v>
       </c>
@@ -3741,7 +3795,7 @@
         <v>3671.1662265988411</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14.036250000000001</v>
       </c>
@@ -3767,7 +3821,7 @@
         <v>3300.9479212045362</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14.079000000000001</v>
       </c>
@@ -3793,7 +3847,7 @@
         <v>2323.6468937799841</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14.104789999999999</v>
       </c>
@@ -6166,20 +6220,23 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.77734375" customWidth="1"/>
-    <col min="7" max="7" width="22.21875" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6199,28 +6256,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>15.84849</v>
       </c>
@@ -6248,8 +6314,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>15.862869999999999</v>
       </c>
@@ -6275,7 +6345,7 @@
         <v>4883.3625809421856</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>15.8726</v>
       </c>
@@ -6301,7 +6371,7 @@
         <v>5672.2071416729823</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>15.90056</v>
       </c>
@@ -6327,7 +6397,7 @@
         <v>5224.6762647910864</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>15.915469999999999</v>
       </c>
@@ -6353,7 +6423,7 @@
         <v>4230.6405022806257</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>15.933669999999999</v>
       </c>
@@ -6379,7 +6449,7 @@
         <v>4432.6277264670734</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>15.944100000000001</v>
       </c>
@@ -6405,7 +6475,7 @@
         <v>5117.151560913192</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>15.971500000000001</v>
       </c>
@@ -6431,7 +6501,7 @@
         <v>3594.8328838880921</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>15.972569999999999</v>
       </c>
@@ -6457,7 +6527,7 @@
         <v>4229.4370332732178</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>15.98197</v>
       </c>
@@ -6483,7 +6553,7 @@
         <v>4751.1267359102203</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>15.996689999999999</v>
       </c>
@@ -6509,7 +6579,7 @@
         <v>3750.5506158193239</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>16.000769999999999</v>
       </c>
@@ -6535,7 +6605,7 @@
         <v>3829.475168463232</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16.045439999999999</v>
       </c>
@@ -6561,7 +6631,7 @@
         <v>4229.6880186107264</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16.063110000000002</v>
       </c>
@@ -6587,7 +6657,7 @@
         <v>3968.0746908142091</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16.078420000000001</v>
       </c>
@@ -8934,20 +9004,23 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:M124"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20.44140625" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8967,28 +9040,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>20.054580000000001</v>
       </c>
@@ -9016,8 +9098,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>20.075959999999998</v>
       </c>
@@ -9043,7 +9129,7 @@
         <v>4210.6393131936748</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>20.095420000000001</v>
       </c>
@@ -9069,7 +9155,7 @@
         <v>3826.112652878699</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>20.097580000000001</v>
       </c>
@@ -9095,7 +9181,7 @@
         <v>4018.2561372971122</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>20.130500000000001</v>
       </c>
@@ -9121,7 +9207,7 @@
         <v>3748.2974676095</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>20.14629</v>
       </c>
@@ -9147,7 +9233,7 @@
         <v>3456.511619698495</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>20.15363</v>
       </c>
@@ -9173,7 +9259,7 @@
         <v>4332.3855997142646</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>20.154869999999999</v>
       </c>
@@ -9199,7 +9285,7 @@
         <v>3422.259660355593</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>20.166830000000001</v>
       </c>
@@ -9225,7 +9311,7 @@
         <v>3540.299505440616</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>20.1675</v>
       </c>
@@ -9251,7 +9337,7 @@
         <v>3729.9030146390278</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>20.172999999999998</v>
       </c>
@@ -9277,7 +9363,7 @@
         <v>4842.6279188308554</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>20.17867</v>
       </c>
@@ -9303,7 +9389,7 @@
         <v>3784.5565370534291</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>20.202960000000001</v>
       </c>
@@ -9329,7 +9415,7 @@
         <v>3436.1697289449121</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>20.225290000000001</v>
       </c>
@@ -9355,7 +9441,7 @@
         <v>4238.7249172285201</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>20.23404</v>
       </c>
@@ -12196,20 +12282,23 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="7" max="7" width="20.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12229,28 +12318,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>333.14209</v>
       </c>
@@ -12278,8 +12376,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>333.17171999999999</v>
       </c>
@@ -12305,7 +12407,7 @@
         <v>3494.8889996972939</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>333.20623999999998</v>
       </c>
@@ -12331,7 +12433,7 @@
         <v>3111.4397717945981</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>333.20900999999998</v>
       </c>
@@ -12357,7 +12459,7 @@
         <v>3365.9486696007812</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>333.21483999999998</v>
       </c>
@@ -12383,7 +12485,7 @@
         <v>3078.2411998346329</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>333.25815</v>
       </c>
@@ -12409,7 +12511,7 @@
         <v>3074.7176738669568</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>333.27938999999998</v>
       </c>
@@ -12435,7 +12537,7 @@
         <v>4622.4056427907253</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>333.28827000000001</v>
       </c>
@@ -12461,7 +12563,7 @@
         <v>2996.532092665424</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>333.33877999999999</v>
       </c>
@@ -12487,7 +12589,7 @@
         <v>2639.6190120442279</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>333.36899</v>
       </c>
@@ -12513,7 +12615,7 @@
         <v>2538.8090480255</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>333.37698</v>
       </c>
@@ -12539,7 +12641,7 @@
         <v>3809.348822109589</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>333.38440000000003</v>
       </c>
@@ -12565,7 +12667,7 @@
         <v>2583.5828723619011</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>333.38852000000003</v>
       </c>
@@ -12591,7 +12693,7 @@
         <v>3195.855731383022</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>333.39382999999998</v>
       </c>
@@ -12617,7 +12719,7 @@
         <v>4898.9355763060285</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>333.42862000000002</v>
       </c>
@@ -14548,20 +14650,23 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14581,28 +14686,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>339.25295999999997</v>
       </c>
@@ -14630,8 +14744,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>339.28314</v>
       </c>
@@ -14657,7 +14775,7 @@
         <v>5339.9702622901559</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>339.32040000000001</v>
       </c>
@@ -14683,7 +14801,7 @@
         <v>5928.2385413151278</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>339.38364000000001</v>
       </c>
@@ -14709,7 +14827,7 @@
         <v>5040.4300523138036</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>339.48876999999999</v>
       </c>
@@ -14735,7 +14853,7 @@
         <v>4776.0213758299124</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>339.57137999999998</v>
       </c>
@@ -14761,7 +14879,7 @@
         <v>4621.73802524031</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>339.65140000000002</v>
       </c>
@@ -14787,7 +14905,7 @@
         <v>4281.5857859562802</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>339.65600999999998</v>
       </c>
@@ -14813,7 +14931,7 @@
         <v>4352.8912192427524</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>339.68704000000002</v>
       </c>
@@ -14839,7 +14957,7 @@
         <v>4304.7843863880153</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>339.72082999999998</v>
       </c>
@@ -14865,7 +14983,7 @@
         <v>4144.223967109242</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>339.72091999999998</v>
       </c>
@@ -14891,7 +15009,7 @@
         <v>4049.517055802216</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>339.84503000000001</v>
       </c>
@@ -14917,7 +15035,7 @@
         <v>4213.9067041052631</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>339.90033</v>
       </c>
@@ -14943,7 +15061,7 @@
         <v>3609.721092163395</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>340.02123999999998</v>
       </c>
@@ -14969,7 +15087,7 @@
         <v>3501.2377545824979</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>340.06664999999998</v>
       </c>
@@ -16744,20 +16862,23 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.88671875" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16777,28 +16898,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>358.10613000000001</v>
       </c>
@@ -16826,8 +16956,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>358.17876000000001</v>
       </c>
@@ -16853,7 +16987,7 @@
         <v>3280.927988249487</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>358.30477999999999</v>
       </c>
@@ -16879,7 +17013,7 @@
         <v>2830.2336883692769</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>358.37065999999999</v>
       </c>
@@ -16905,7 +17039,7 @@
         <v>2970.789283655497</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>358.52202999999997</v>
       </c>
@@ -16931,7 +17065,7 @@
         <v>4639.9145945233058</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>358.62263000000002</v>
       </c>
@@ -16957,7 +17091,7 @@
         <v>2208.43545126866</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>358.68509999999998</v>
       </c>
@@ -16983,7 +17117,7 @@
         <v>1713.050694192397</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>358.68869000000001</v>
       </c>
@@ -17009,7 +17143,7 @@
         <v>2042.028926602336</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>358.71370000000002</v>
       </c>
@@ -17035,7 +17169,7 @@
         <v>1412.753915133045</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>358.73047000000003</v>
       </c>
@@ -17061,7 +17195,7 @@
         <v>2795.6822614658658</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>358.75092000000001</v>
       </c>
@@ -17087,7 +17221,7 @@
         <v>1431.3325470466691</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>358.77641</v>
       </c>
@@ -17113,7 +17247,7 @@
         <v>2566.3068524237642</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>358.89868000000001</v>
       </c>
@@ -17139,7 +17273,7 @@
         <v>2191.4937936909901</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>358.91721999999999</v>
       </c>
@@ -17165,7 +17299,7 @@
         <v>2006.8149435988489</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>358.91755999999998</v>
       </c>
@@ -18083,7 +18217,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
@@ -18092,11 +18226,14 @@
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18116,28 +18253,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>12.837529999999999</v>
       </c>
@@ -18165,8 +18311,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>12.979039999999999</v>
       </c>
@@ -18192,7 +18342,7 @@
         <v>3809.7594668901302</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>12.98714</v>
       </c>
@@ -18218,7 +18368,7 @@
         <v>2702.8279856309741</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>13.037750000000001</v>
       </c>
@@ -18244,7 +18394,7 @@
         <v>4560.1485188600609</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>13.06771</v>
       </c>
@@ -18270,7 +18420,7 @@
         <v>2877.6009448270761</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>13.07014</v>
       </c>
@@ -18296,7 +18446,7 @@
         <v>1614.7746438771869</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>13.08755</v>
       </c>
@@ -18322,7 +18472,7 @@
         <v>1708.9571439913871</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>13.09613</v>
       </c>
@@ -18348,7 +18498,7 @@
         <v>1349.6775404015259</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>13.11436</v>
       </c>
@@ -18374,7 +18524,7 @@
         <v>1205.8099314248871</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>13.13477</v>
       </c>
@@ -18400,7 +18550,7 @@
         <v>1053.998440831459</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>13.13951</v>
       </c>
@@ -18426,7 +18576,7 @@
         <v>1079.9999811065641</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13.14555</v>
       </c>
@@ -18452,7 +18602,7 @@
         <v>988.80507218147693</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13.152979999999999</v>
       </c>
@@ -18478,7 +18628,7 @@
         <v>987.87165804308802</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13.16023</v>
       </c>
@@ -18504,7 +18654,7 @@
         <v>3377.8290068682222</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13.170680000000001</v>
       </c>
@@ -19083,7 +19233,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.77734375" customWidth="1"/>
@@ -19091,12 +19241,15 @@
     <col min="8" max="8" width="12.21875" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
-    <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="12" width="20.21875" customWidth="1"/>
+    <col min="13" max="13" width="23.44140625" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" customWidth="1"/>
+    <col min="15" max="15" width="25.5546875" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19116,28 +19269,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>40.127859999999998</v>
       </c>
@@ -19165,8 +19327,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>40.139220000000002</v>
       </c>
@@ -19192,7 +19358,7 @@
         <v>3533.087052756302</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>40.147910000000003</v>
       </c>
@@ -19218,7 +19384,7 @@
         <v>3514.280042399932</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>40.16789</v>
       </c>
@@ -19244,7 +19410,7 @@
         <v>3460.4764827104191</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>40.169040000000003</v>
       </c>
@@ -19270,7 +19436,7 @@
         <v>5701.753487106711</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>40.170400000000001</v>
       </c>
@@ -19296,7 +19462,7 @@
         <v>3814.1768307805528</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>40.195709999999998</v>
       </c>
@@ -19322,7 +19488,7 @@
         <v>4324.9004520277658</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>40.215130000000002</v>
       </c>
@@ -19348,7 +19514,7 @@
         <v>3074.3024497507731</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>40.225569999999998</v>
       </c>
@@ -19374,7 +19540,7 @@
         <v>3831.5037899356871</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>40.228670000000001</v>
       </c>
@@ -19400,7 +19566,7 @@
         <v>3451.0146230602159</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>40.244660000000003</v>
       </c>
@@ -19426,7 +19592,7 @@
         <v>4031.5785464243759</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>40.253120000000003</v>
       </c>
@@ -19452,7 +19618,7 @@
         <v>3312.9449006925911</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>40.257100000000001</v>
       </c>
@@ -19478,7 +19644,7 @@
         <v>2769.0955193368932</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>40.273229999999998</v>
       </c>
@@ -19504,7 +19670,7 @@
         <v>2625.909575713591</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>40.282780000000002</v>
       </c>
@@ -21721,20 +21887,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -21754,28 +21923,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>64.625420000000005</v>
       </c>
@@ -21803,8 +21981,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>64.663380000000004</v>
       </c>
@@ -21830,7 +22012,7 @@
         <v>4471.9891085524296</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>64.695629999999994</v>
       </c>
@@ -21856,7 +22038,7 @@
         <v>4268.7918957545889</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>64.71875</v>
       </c>
@@ -21882,7 +22064,7 @@
         <v>5254.0860299450751</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>64.743799999999993</v>
       </c>
@@ -21908,7 +22090,7 @@
         <v>4537.9328876869249</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>64.746170000000006</v>
       </c>
@@ -21934,7 +22116,7 @@
         <v>3835.0045453368521</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>64.790700000000001</v>
       </c>
@@ -21960,7 +22142,7 @@
         <v>3412.771807660843</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>64.797790000000006</v>
       </c>
@@ -21986,7 +22168,7 @@
         <v>4963.4886192186577</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>64.811040000000006</v>
       </c>
@@ -22012,7 +22194,7 @@
         <v>5197.2241011396118</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>64.811329999999998</v>
       </c>
@@ -22038,7 +22220,7 @@
         <v>4644.636811781239</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>64.812129999999996</v>
       </c>
@@ -22064,7 +22246,7 @@
         <v>3289.468410426392</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>64.823710000000005</v>
       </c>
@@ -22090,7 +22272,7 @@
         <v>4479.4626738837051</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>64.824169999999995</v>
       </c>
@@ -22116,7 +22298,7 @@
         <v>3159.7207198888741</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>64.83108</v>
       </c>
@@ -22142,7 +22324,7 @@
         <v>4369.6911633817836</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>64.839960000000005</v>
       </c>
@@ -23995,20 +24177,23 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24028,28 +24213,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1.6240399999999999</v>
       </c>
@@ -24077,8 +24271,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1.6389199999999999</v>
       </c>
@@ -24104,7 +24302,7 @@
         <v>3277.9810979249778</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1.6877500000000001</v>
       </c>
@@ -24130,7 +24328,7 @@
         <v>3677.3986457039218</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1.6932100000000001</v>
       </c>
@@ -24156,7 +24354,7 @@
         <v>3905.3774661100229</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1.70217</v>
       </c>
@@ -24182,7 +24380,7 @@
         <v>3497.1066360768209</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1.7446699999999999</v>
       </c>
@@ -24208,7 +24406,7 @@
         <v>3676.013594517523</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1.76183</v>
       </c>
@@ -24234,7 +24432,7 @@
         <v>2802.416459452797</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1.79508</v>
       </c>
@@ -24260,7 +24458,7 @@
         <v>2664.9769061944521</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1.81463</v>
       </c>
@@ -24286,7 +24484,7 @@
         <v>3663.9525342947509</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1.83796</v>
       </c>
@@ -24312,7 +24510,7 @@
         <v>2563.5505662136152</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1.8420399999999999</v>
       </c>
@@ -24338,7 +24536,7 @@
         <v>3263.723398207268</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1.87571</v>
       </c>
@@ -24364,7 +24562,7 @@
         <v>3266.8701267855758</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1.89158</v>
       </c>
@@ -24390,7 +24588,7 @@
         <v>2257.402872840858</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1.93438</v>
       </c>
@@ -24416,7 +24614,7 @@
         <v>2138.8858280495479</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.9426699999999999</v>
       </c>
@@ -26763,20 +26961,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.33203125" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26796,28 +26997,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>6.0337899999999998</v>
       </c>
@@ -26845,8 +27055,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>6.0639500000000002</v>
       </c>
@@ -26872,7 +27086,7 @@
         <v>5221.1579088483422</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>6.0800700000000001</v>
       </c>
@@ -26898,7 +27112,7 @@
         <v>3474.2903870933651</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>6.1306500000000002</v>
       </c>
@@ -26924,7 +27138,7 @@
         <v>4326.4675244160389</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6.1502999999999997</v>
       </c>
@@ -26950,7 +27164,7 @@
         <v>3809.0367797750018</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6.2211100000000004</v>
       </c>
@@ -26976,7 +27190,7 @@
         <v>3833.1574986442288</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6.2258899999999997</v>
       </c>
@@ -27002,7 +27216,7 @@
         <v>2736.0638854030599</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6.2521300000000002</v>
       </c>
@@ -27028,7 +27242,7 @@
         <v>2607.5598349491129</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6.2834399999999997</v>
       </c>
@@ -27054,7 +27268,7 @@
         <v>4065.7647943010811</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6.3405500000000004</v>
       </c>
@@ -27080,7 +27294,7 @@
         <v>2041.4125905260121</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6.3646200000000004</v>
       </c>
@@ -27106,7 +27320,7 @@
         <v>5429.6488767536202</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6.3714500000000003</v>
       </c>
@@ -27132,7 +27346,7 @@
         <v>2420.951004023867</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6.3805500000000004</v>
       </c>
@@ -27158,7 +27372,7 @@
         <v>1349.722290500509</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>6.3839899999999998</v>
       </c>
@@ -27184,7 +27398,7 @@
         <v>1235.9243036423291</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6.4218799999999998</v>
       </c>
@@ -28075,20 +28289,23 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -28108,28 +28325,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>7.44421</v>
       </c>
@@ -28157,8 +28383,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>7.4700300000000004</v>
       </c>
@@ -28184,7 +28414,7 @@
         <v>5226.8107387161854</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>7.57409</v>
       </c>
@@ -28210,7 +28440,7 @@
         <v>3309.4675659468089</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>7.6036200000000003</v>
       </c>
@@ -28236,7 +28466,7 @@
         <v>3489.0591028451008</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>7.6438899999999999</v>
       </c>
@@ -28262,7 +28492,7 @@
         <v>3606.6370978559171</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7.7073900000000002</v>
       </c>
@@ -28288,7 +28518,7 @@
         <v>3246.358609935573</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7.7310499999999998</v>
       </c>
@@ -28314,7 +28544,7 @@
         <v>2913.8780089689189</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7.7568900000000003</v>
       </c>
@@ -28340,7 +28570,7 @@
         <v>3645.138978072353</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7.9202899999999996</v>
       </c>
@@ -28366,7 +28596,7 @@
         <v>2554.6123717858568</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>7.9295400000000003</v>
       </c>
@@ -28392,7 +28622,7 @@
         <v>1939.0712356690681</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>8.0060400000000005</v>
       </c>
@@ -28418,7 +28648,7 @@
         <v>1667.263779716614</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>8.0084400000000002</v>
       </c>
@@ -28444,7 +28674,7 @@
         <v>1632.808602916713</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>8.0089000000000006</v>
       </c>
@@ -28470,7 +28700,7 @@
         <v>1720.482489983988</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>8.0175699999999992</v>
       </c>
@@ -28496,7 +28726,7 @@
         <v>3353.4113917544491</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>8.0667000000000009</v>
       </c>
@@ -29387,20 +29617,23 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -29420,28 +29653,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>8.0830800000000007</v>
       </c>
@@ -29469,8 +29711,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>8.1003799999999995</v>
       </c>
@@ -29496,7 +29742,7 @@
         <v>4348.1807259203888</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>8.1181300000000007</v>
       </c>
@@ -29522,7 +29768,7 @@
         <v>5191.4097084933665</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>8.1341199999999994</v>
       </c>
@@ -29548,7 +29794,7 @@
         <v>4674.6464335358733</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>8.1635799999999996</v>
       </c>
@@ -29574,7 +29820,7 @@
         <v>4038.4024632972919</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8.1705799999999993</v>
       </c>
@@ -29600,7 +29846,7 @@
         <v>4158.1220023844999</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8.2916299999999996</v>
       </c>
@@ -29626,7 +29872,7 @@
         <v>4689.8966449484305</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8.3122500000000006</v>
       </c>
@@ -29652,7 +29898,7 @@
         <v>4541.3867276261644</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8.3171700000000008</v>
       </c>
@@ -29678,7 +29924,7 @@
         <v>4231.5299439533401</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8.3767899999999997</v>
       </c>
@@ -29704,7 +29950,7 @@
         <v>3629.3887262187991</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>8.4069599999999998</v>
       </c>
@@ -29730,7 +29976,7 @@
         <v>3943.0866435928988</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>8.4079200000000007</v>
       </c>
@@ -29756,7 +30002,7 @@
         <v>3893.5354698384858</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>8.4307099999999995</v>
       </c>
@@ -29782,7 +30028,7 @@
         <v>3782.6011779230189</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>8.44102</v>
       </c>
@@ -29808,7 +30054,7 @@
         <v>4334.5879536437023</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>8.4814500000000006</v>
       </c>
@@ -32545,20 +32791,23 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -32578,28 +32827,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>9.3267000000000007</v>
       </c>
@@ -32627,8 +32885,12 @@
       <c r="I2" s="1">
         <v>4.3019999999999996E-6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <f>(0.7*L2) * 0.093 * (((0.7*L2) / (200000000000000 / 0.7)) ^ 0.21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>9.3640500000000007</v>
       </c>
@@ -32654,7 +32916,7 @@
         <v>5312.4492394328618</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>9.4048499999999997</v>
       </c>
@@ -32680,7 +32942,7 @@
         <v>4000.5532805450498</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>9.5771499999999996</v>
       </c>
@@ -32706,7 +32968,7 @@
         <v>3482.1876766941832</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>9.6131399999999996</v>
       </c>
@@ -32732,7 +32994,7 @@
         <v>3861.7132164115242</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>9.7006700000000006</v>
       </c>
@@ -32758,7 +33020,7 @@
         <v>6027.6874031572061</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>9.7676200000000009</v>
       </c>
@@ -32784,7 +33046,7 @@
         <v>3920.708055246439</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9.8136100000000006</v>
       </c>
@@ -32810,7 +33072,7 @@
         <v>3930.240226950747</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9.8403399999999994</v>
       </c>
@@ -32836,7 +33098,7 @@
         <v>3650.0448132513529</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9.9302499999999991</v>
       </c>
@@ -32862,7 +33124,7 @@
         <v>3439.5764019776138</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10.19871</v>
       </c>
@@ -32888,7 +33150,7 @@
         <v>2621.733078469405</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10.23781</v>
       </c>
@@ -32914,7 +33176,7 @@
         <v>1665.197374153151</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>10.2996</v>
       </c>
@@ -32940,7 +33202,7 @@
         <v>1437.478165497075</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>10.31945</v>
       </c>
@@ -32966,7 +33228,7 @@
         <v>2660.6590393286879</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>10.45811</v>
       </c>

--- a/App/dataset/Cluster_dataset.xlsx
+++ b/App/dataset/Cluster_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elyon\OneDrive\Desktop\phd_PE\dark_matter_notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31693393-585C-4C05-A8C0-64866A31FF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E933567A-93E0-4478-883F-903E80A0B5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abell0080" sheetId="1" r:id="rId1"/>
@@ -49,59 +49,190 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="16">
   <si>
-    <t>Radeg</t>
-  </si>
-  <si>
-    <t>Dedeg</t>
-  </si>
-  <si>
-    <t>Velocity_Gal (km/s)</t>
-  </si>
-  <si>
-    <t>err_RV</t>
-  </si>
-  <si>
     <t>q_RV</t>
   </si>
   <si>
-    <t>bmag</t>
+    <t>Radius[kpc]</t>
   </si>
   <si>
-    <t>Radius_kpc</t>
+    <t>Velocity Error</t>
   </si>
   <si>
-    <t>G [kpc*(km/s)^2/M_sun]</t>
+    <t>Right Ascension [deg]</t>
   </si>
   <si>
-    <t>Total_Mass [M_sun]</t>
+    <t>Declination [deg]</t>
   </si>
   <si>
-    <t>Standard_Deviation (km/s)</t>
+    <t>Galaxy Velocity [km/s]</t>
   </si>
   <si>
-    <t>Star_Mass_Msun</t>
+    <t xml:space="preserve">Mean Radius [kpc] </t>
   </si>
   <si>
-    <t xml:space="preserve">Mean_Radius [kpc] </t>
+    <t>Luminous Mass[Solar Mass]</t>
   </si>
   <si>
-    <t>Gas_Mass[M_sun]</t>
+    <t>Total Mass/Luminous Mass</t>
   </si>
   <si>
-    <t>Star_Mass_Tot [M_sun]</t>
+    <t>Standard Deviation [km/s]</t>
   </si>
   <si>
-    <t>Luminous_Mass[M_sun]</t>
+    <t>Apparent Magnitude[mag ]</t>
   </si>
   <si>
-    <t>Tot_Mass/Lum_Mass</t>
+    <r>
+      <t>Stellar Mass [M</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>☉</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>G [kpc*(km/s)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/M</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>☉</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Gas Mass[M</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>☉</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Stellar Mass [M</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>☉</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Mass [M</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>☉</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +253,29 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -545,72 +699,71 @@
   <dimension ref="A1:P108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
-    <col min="11" max="11" width="24.5546875" customWidth="1"/>
-    <col min="12" max="12" width="19.109375" customWidth="1"/>
-    <col min="13" max="13" width="23.21875" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" customWidth="1"/>
-    <col min="15" max="15" width="22.88671875" customWidth="1"/>
-    <col min="16" max="16" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -3413,67 +3566,71 @@
   <dimension ref="A1:P106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -6223,67 +6380,71 @@
   <dimension ref="A1:P105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="19.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -9007,67 +9168,71 @@
   <dimension ref="A1:P124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -12285,67 +12450,71 @@
   <dimension ref="A1:P89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -14653,67 +14822,71 @@
   <dimension ref="A1:P83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -16857,6 +17030,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16865,67 +17039,71 @@
   <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -18220,67 +18398,71 @@
   <dimension ref="A1:P37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -19236,67 +19418,71 @@
   <dimension ref="A1:P100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="23.21875" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
-    <col min="11" max="11" width="26" customWidth="1"/>
-    <col min="12" max="12" width="20.21875" customWidth="1"/>
-    <col min="13" max="13" width="23.44140625" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" customWidth="1"/>
-    <col min="15" max="15" width="25.5546875" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -21890,67 +22076,71 @@
   <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -24180,67 +24370,71 @@
   <dimension ref="A1:P105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -26964,67 +27158,71 @@
   <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -28292,67 +28490,71 @@
   <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -29620,67 +29822,71 @@
   <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -32794,67 +33000,71 @@
   <dimension ref="A1:P48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
